--- a/Code_To_Visualizer_Project_Plan.xlsx
+++ b/Code_To_Visualizer_Project_Plan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ranjanbabu\Downloads\code-to-visualizer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JESH\Downloads\code_to_visualizer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6CBF7F-6984-4EF4-8080-473C7C168BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45323055-AFEA-4BF6-89D3-50503EA466EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Plan" sheetId="1" r:id="rId1"/>
@@ -76,53 +76,53 @@
     <t>ER Diagram</t>
   </si>
   <si>
-    <t>Registration Page Module</t>
-  </si>
-  <si>
-    <t>Technician Availability &amp; Assignment Module</t>
-  </si>
-  <si>
-    <t>Service Booking &amp; Scheduling Module</t>
-  </si>
-  <si>
-    <t>GPS-Based Technician Tracking Module</t>
-  </si>
-  <si>
-    <t>Rating &amp; Review System Module</t>
-  </si>
-  <si>
-    <t>Product Catalog &amp; Comparison Module</t>
-  </si>
-  <si>
-    <t>Old Appliance Exchange Module</t>
-  </si>
-  <si>
-    <t>Admin Control Module</t>
-  </si>
-  <si>
-    <t>Reports &amp; Analytics Module</t>
-  </si>
-  <si>
-    <t>Complaint &amp; Escalation Module</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
-    <t>Implementation</t>
-  </si>
-  <si>
     <t>Project Title: RAGSY - CODE TO VISUALIZER</t>
   </si>
   <si>
     <t>Members: RANJANBABU,YOGESH,SHWETHA,GOUTHAM,AKLIMA BEGUM SARA</t>
+  </si>
+  <si>
+    <t>Authentication Module</t>
+  </si>
+  <si>
+    <t>Flowchart Engine (AST Parser)</t>
+  </si>
+  <si>
+    <t>Code Editor &amp; Execution Engine</t>
+  </si>
+  <si>
+    <t>Flowchart Rendering (React Flow)</t>
+  </si>
+  <si>
+    <t>Forgot Password &amp; SMS OTP</t>
+  </si>
+  <si>
+    <t>Code Encryption (AES-256 Fernet)</t>
+  </si>
+  <si>
+    <t>Admin Dashboard Module</t>
+  </si>
+  <si>
+    <t>JavaScript Basics Support</t>
+  </si>
+  <si>
+    <t>Task List &amp; Learning Feature</t>
+  </si>
+  <si>
+    <t>Dagre Layout &amp; PNG Export Fix</t>
+  </si>
+  <si>
+    <t>Implementation / Deployment</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,8 +130,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,13 +155,40 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -164,13 +197,17 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,326 +513,326 @@
   <dimension ref="A1:Z24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45" style="2" customWidth="1"/>
-    <col min="2" max="25" width="4" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="45" customWidth="1"/>
+    <col min="2" max="25" width="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" t="s">
+        <v>10</v>
+      </c>
+      <c r="M6" t="s">
+        <v>11</v>
+      </c>
+      <c r="N6" t="s">
+        <v>8</v>
+      </c>
+      <c r="O6" t="s">
+        <v>9</v>
+      </c>
+      <c r="P6" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>11</v>
+      </c>
+      <c r="R6" t="s">
+        <v>8</v>
+      </c>
+      <c r="S6" t="s">
+        <v>9</v>
+      </c>
+      <c r="T6" t="s">
+        <v>10</v>
+      </c>
+      <c r="U6" t="s">
+        <v>11</v>
+      </c>
+      <c r="V6" t="s">
+        <v>8</v>
+      </c>
+      <c r="W6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X6" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="1"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O18" s="1"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q20" s="1"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="R21" s="1"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="S22" s="1"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="X6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L15" s="4"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" s="4"/>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N17" s="4"/>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O18" s="4"/>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P19" s="4"/>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q20" s="4"/>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="R21" s="5"/>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="S22" s="5"/>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="V24" s="4"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="9">
